--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791505</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791504</v>
       </c>
       <c r="B3" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,49 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135791504</v>
+        <v>136423275</v>
       </c>
       <c r="B3" t="n">
-        <v>99244</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bryngelhögen, Jmt</t>
+          <t>Lövbergsflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476170</v>
+        <v>476393</v>
       </c>
       <c r="R3" t="n">
-        <v>6920769</v>
+        <v>6920610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,16 +891,127 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136423275</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135791504</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99244</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bryngelhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476170</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6920769</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135791504</t>
         </is>
@@ -904,6 +1021,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>135791504</v>
       </c>
       <c r="B4" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32280-2026 artfynd.xlsx
+++ b/artfynd/A 32280-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136423275</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
